--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6650-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6650-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23375B90-8D72-447A-A720-FF9B7AACDCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD008D94-57A5-43C6-AB4B-9222A9F8DF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E9035132-4B2C-4092-973F-F9BA82AC7D3E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{08818D9A-16EE-4789-AAE8-515BE31DDC06}"/>
   </bookViews>
   <sheets>
     <sheet name="6650-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1496,20 +1496,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B82B331-5C38-44A4-BD11-2557DB932969}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C46EC9-71EA-485E-936E-4135E00D03FC}">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1663,7 +1663,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="41">
         <v>2023</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
         <v>26</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="44"/>
       <c r="B16" s="22" t="s">
         <v>37</v>
@@ -2293,7 +2293,7 @@
       <c r="Q16" s="48"/>
       <c r="R16" s="48"/>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2022</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>2021</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2020</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2019</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2018</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>38</v>
       </c>
